--- a/Dev_GNC/TableData/MonsterDataTable.xlsx
+++ b/Dev_GNC/TableData/MonsterDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA282205-D6DA-4756-8980-28A89EB92C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CA662F-C4E6-4E65-A0A0-C90EFA03322F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42480" yWindow="2760" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -52,43 +52,31 @@
     <t>sight</t>
   </si>
   <si>
-    <t>prefabPath</t>
-  </si>
-  <si>
-    <t>projectilePath</t>
-  </si>
-  <si>
     <t>monster_slime</t>
   </si>
   <si>
     <t>슬라임</t>
   </si>
   <si>
-    <t>Prefabs/Actor/Monster/Monster_Slime</t>
-  </si>
-  <si>
     <t>monster_turtle</t>
   </si>
   <si>
     <t>거북이</t>
   </si>
   <si>
-    <t>Prefabs/Actor/Monster/Monster_Turtle</t>
-  </si>
-  <si>
     <t>gold</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>exp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -99,12 +87,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -147,15 +129,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -376,10 +357,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -410,103 +391,91 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>19</v>
+      <c r="D2" s="2">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4">
+        <v>50</v>
+      </c>
+      <c r="L2" s="4">
+        <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="G3" s="2">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
         <v>4</v>
       </c>
-      <c r="H2" s="3">
-        <v>5</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3">
-        <v>5</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="5">
-        <v>50</v>
-      </c>
-      <c r="N2" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3">
-        <v>15</v>
-      </c>
-      <c r="E3" s="3">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
-        <v>3</v>
-      </c>
-      <c r="H3" s="3">
-        <v>5</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3">
-        <v>4</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="5">
+      <c r="K3" s="4">
         <v>100</v>
       </c>
-      <c r="N3" s="5">
+      <c r="L3" s="4">
         <v>100</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Dev_GNC/TableData/MonsterDataTable.xlsx
+++ b/Dev_GNC/TableData/MonsterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealProjects\ProjectGNC\Dev_GNC\TableData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82CA662F-C4E6-4E65-A0A0-C90EFA03322F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291AFCA8-1964-4D5A-A79F-1ACA068B1383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42480" yWindow="2760" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39180" yWindow="2460" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
     <t>idAlias</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>hp</t>
   </si>
   <si>
@@ -69,6 +66,10 @@
   </si>
   <si>
     <t>exp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nameAlias</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -129,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -139,6 +140,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -367,35 +369,35 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="K1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -403,10 +405,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="D2" s="2">
         <v>10</v>
@@ -441,10 +443,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="D3" s="2">
         <v>15</v>
